--- a/model/data/invoice/sale-invoices-from-digikala/1405-04-21-sale-zibavash-express.xlsx
+++ b/model/data/invoice/sale-invoices-from-digikala/1405-04-21-sale-zibavash-express.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>شیوه ارسال مرسوله</t>
   </si>
@@ -100,55 +100,76 @@
     <t>-</t>
   </si>
   <si>
-    <t>رژ لب مایع</t>
-  </si>
-  <si>
-    <t>رژ لب مایع گلدن رز شماره 43 | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
     <t>1روز</t>
   </si>
   <si>
-    <t>1405/03/20</t>
-  </si>
-  <si>
-    <t>1405/03/21</t>
-  </si>
-  <si>
-    <t>مازندران-نور</t>
-  </si>
-  <si>
-    <t>در حال ارسال</t>
-  </si>
-  <si>
-    <t>210160508300009570464147</t>
-  </si>
-  <si>
-    <t>راحله اردی</t>
-  </si>
-  <si>
-    <t>ج آمل چمستان، ج سالده, پلاک ۲۰</t>
-  </si>
-  <si>
-    <t>09115824458</t>
-  </si>
-  <si>
-    <t>کرم پودر</t>
-  </si>
-  <si>
-    <t>کرم پودر گلدن رز مدل Matte Perfection شماره W4 حجم 35 میلی لیتر | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
-    <t>هرمزگان-بندرعباس</t>
-  </si>
-  <si>
-    <t>rana hashemi</t>
-  </si>
-  <si>
-    <t>کوی خلیج فارس، بل پردیس، بعد از چهارراه پردیس، خ. پردیس، ک. پردیس4, پلاک ۲۵, واحد ۲۵</t>
-  </si>
-  <si>
-    <t>09335217745</t>
+    <t>ژل و صابون ابرو</t>
+  </si>
+  <si>
+    <t>ژل ابرو کولمار مدل آرگان دار | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>1405/04/18</t>
+  </si>
+  <si>
+    <t>1405/04/21</t>
+  </si>
+  <si>
+    <t>گیلان-رشت</t>
+  </si>
+  <si>
+    <t>در انتظار جمع آوری</t>
+  </si>
+  <si>
+    <t>مینا میکاییلی</t>
+  </si>
+  <si>
+    <t>پستک، خ. استاد معین، کوچه شهید میزاده،فرعی بهار ساختمان مازیار , پلاک ندارم</t>
+  </si>
+  <si>
+    <t>09396093165</t>
+  </si>
+  <si>
+    <t>1405/04/20</t>
+  </si>
+  <si>
+    <t>تهران-تهران</t>
+  </si>
+  <si>
+    <t>خط چشم</t>
+  </si>
+  <si>
+    <t>خط چشم گلدن رز مدل EYELINER | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>شراره راستیفر</t>
+  </si>
+  <si>
+    <t>سعادت آباد، بل دادمان، بعد از خ. درختی، نبش خ. فایز دشتی, پلاک ۴, واحد ۲</t>
+  </si>
+  <si>
+    <t>09123491472</t>
+  </si>
+  <si>
+    <t>مداد لب</t>
+  </si>
+  <si>
+    <t>مداد لب گلدن رز مدل DREAM شماره 519 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>سیستان و بلوچستان-زاهدان</t>
+  </si>
+  <si>
+    <t>سمانه كياني</t>
+  </si>
+  <si>
+    <t>رودکی، خ. بدر، خ. بدر39، خ. رودکی18</t>
+  </si>
+  <si>
+    <t>09216951905</t>
   </si>
 </sst>
 </file>
@@ -498,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -597,35 +618,35 @@
         <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1">
-        <v>10618527</v>
+        <v>15831542</v>
       </c>
       <c r="E2" s="1">
-        <v>38091065</v>
+        <v>63117035</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
-        <v>358901422</v>
+        <v>363271044</v>
       </c>
       <c r="H2" s="1">
-        <v>364557441</v>
+        <v>369454416</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="K2" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2" s="1">
-        <v>7794700</v>
+        <v>4180000</v>
       </c>
       <c r="M2" s="1">
         <v>1390000</v>
@@ -651,20 +672,18 @@
       <c r="T2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="1"/>
+      <c r="V2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1">
+        <v>4169837344</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="X2" s="1">
-        <v>4643473765</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -672,26 +691,26 @@
         <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1">
-        <v>13235102</v>
+        <v>1051842</v>
       </c>
       <c r="E3" s="1">
-        <v>45754984</v>
+        <v>33859103</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
-        <v>358903913</v>
+        <v>363434942</v>
       </c>
       <c r="H3" s="1">
-        <v>364560520</v>
+        <v>369636047</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>26</v>
@@ -700,13 +719,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>8435200</v>
+        <v>3453100</v>
       </c>
       <c r="M3" s="1">
         <v>1390000</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>27</v>
@@ -718,7 +737,7 @@
         <v>32</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>26</v>
@@ -728,16 +747,89 @@
       </c>
       <c r="U3" s="1"/>
       <c r="V3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X3" s="1">
-        <v>7939167499</v>
+        <v>1468663553</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1051594</v>
+      </c>
+      <c r="E4" s="1">
+        <v>37200241</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>363577592</v>
+      </c>
+      <c r="H4" s="1">
+        <v>369801970</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2457700</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1390000</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="1">
+        <v>9817779515</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
